--- a/docs/qa/upload-templates/cost_data_upload_template.xlsx
+++ b/docs/qa/upload-templates/cost_data_upload_template.xlsx
@@ -136,6 +136,11 @@
         <t>Numeric &gt;= 0</t>
       </text>
     </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>standard|actual|purchase</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -429,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,6 +453,21 @@
           <t>currency</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>cost_type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>effective_from</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>standard_cost</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -463,6 +483,19 @@
           <t>USD</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>45000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -478,6 +511,19 @@
           <t>USD</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>85000</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -492,6 +538,19 @@
         <is>
           <t>USD</t>
         </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
